--- a/[LOGage2026] File 01_SKU Master Data.xlsx
+++ b/[LOGage2026] File 01_SKU Master Data.xlsx
@@ -12,7 +12,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="kBmIoYWVfk2BQwXIKG4rCRLNe1KcjeD69MuJzGQLmSk="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="bIKgppUymYAQZt09ZNi9J0VdNvJXysCAmBZW/PyNHv4="/>
     </ext>
   </extLst>
 </workbook>
